--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A606882-FE57-43EA-BD8B-4758FD261AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B757D9-F41C-4885-8058-64D0AD250830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>LP</t>
   </si>
@@ -28,151 +28,289 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-051656</t>
-  </si>
-  <si>
-    <t>Encerrado!</t>
-  </si>
-  <si>
-    <t>LP-051659</t>
-  </si>
-  <si>
-    <t>LP-051686</t>
-  </si>
-  <si>
-    <t>LP-051687</t>
-  </si>
-  <si>
-    <t>LP-051736</t>
-  </si>
-  <si>
-    <t>LP-051754</t>
-  </si>
-  <si>
-    <t>LP-051902</t>
-  </si>
-  <si>
-    <t>LP-051930</t>
-  </si>
-  <si>
-    <t>LP-051966</t>
-  </si>
-  <si>
-    <t>LP-052076</t>
-  </si>
-  <si>
-    <t>LP-044151</t>
-  </si>
-  <si>
-    <t>LP-049891</t>
-  </si>
-  <si>
-    <t>LP-050367</t>
-  </si>
-  <si>
-    <t>LP-050501</t>
-  </si>
-  <si>
-    <t>LP-051494</t>
-  </si>
-  <si>
-    <t>LP-051495</t>
-  </si>
-  <si>
-    <t>LP-051599</t>
-  </si>
-  <si>
-    <t>LP-050001</t>
-  </si>
-  <si>
-    <t>LP-051497</t>
-  </si>
-  <si>
-    <t>LP-051680</t>
-  </si>
-  <si>
-    <t>LP-051682</t>
-  </si>
-  <si>
-    <t>LP-051683</t>
-  </si>
-  <si>
-    <t>LP-051685</t>
-  </si>
-  <si>
-    <t>LP-051709</t>
-  </si>
-  <si>
-    <t>LP-051745</t>
-  </si>
-  <si>
-    <t>LP-051746</t>
-  </si>
-  <si>
-    <t>LP-051749</t>
-  </si>
-  <si>
-    <t>LP-051750</t>
-  </si>
-  <si>
-    <t>LP-051883</t>
-  </si>
-  <si>
-    <t>LP-051884</t>
-  </si>
-  <si>
-    <t>LP-051887</t>
-  </si>
-  <si>
-    <t>LP-051903</t>
-  </si>
-  <si>
-    <t>LP-051904</t>
-  </si>
-  <si>
-    <t>LP-051905</t>
-  </si>
-  <si>
-    <t>LP-051906</t>
-  </si>
-  <si>
-    <t>LP-051907</t>
-  </si>
-  <si>
-    <t>LP-051908</t>
-  </si>
-  <si>
-    <t>LP-051909</t>
-  </si>
-  <si>
-    <t>LP-051910</t>
-  </si>
-  <si>
-    <t>LP-052008</t>
-  </si>
-  <si>
-    <t>LP-052009</t>
-  </si>
-  <si>
-    <t>LP-052017</t>
-  </si>
-  <si>
-    <t>LP-052018</t>
-  </si>
-  <si>
-    <t>LP-052153</t>
-  </si>
-  <si>
-    <t>LP-048713</t>
-  </si>
-  <si>
-    <t>LP-048714</t>
-  </si>
-  <si>
-    <t>LP-047807</t>
-  </si>
-  <si>
-    <t>LP-047806</t>
+    <t>LP-048854</t>
+  </si>
+  <si>
+    <t>LP-049319</t>
+  </si>
+  <si>
+    <t>LP-049320</t>
+  </si>
+  <si>
+    <t>LP-049339</t>
+  </si>
+  <si>
+    <t>LP-049352</t>
+  </si>
+  <si>
+    <t>LP-049373</t>
+  </si>
+  <si>
+    <t>LP-049394</t>
+  </si>
+  <si>
+    <t>LP-050231</t>
+  </si>
+  <si>
+    <t>LP-050423</t>
+  </si>
+  <si>
+    <t>LP-050730</t>
+  </si>
+  <si>
+    <t>LP-050758</t>
+  </si>
+  <si>
+    <t>LP-051393</t>
+  </si>
+  <si>
+    <t>LP-051513</t>
+  </si>
+  <si>
+    <t>LP-051812</t>
+  </si>
+  <si>
+    <t>LP-052014</t>
+  </si>
+  <si>
+    <t>LP-052063</t>
+  </si>
+  <si>
+    <t>LP-052128</t>
+  </si>
+  <si>
+    <t>LP-052248</t>
+  </si>
+  <si>
+    <t>LP-052314</t>
+  </si>
+  <si>
+    <t>LP-052316</t>
+  </si>
+  <si>
+    <t>LP-052319</t>
+  </si>
+  <si>
+    <t>LP-052320</t>
+  </si>
+  <si>
+    <t>LP-052733</t>
+  </si>
+  <si>
+    <t>LP-052736</t>
+  </si>
+  <si>
+    <t>LP-052755</t>
+  </si>
+  <si>
+    <t>LP-052786</t>
+  </si>
+  <si>
+    <t>LP-052787</t>
+  </si>
+  <si>
+    <t>LP-052790</t>
+  </si>
+  <si>
+    <t>LP-052908</t>
+  </si>
+  <si>
+    <t>LP-053101</t>
+  </si>
+  <si>
+    <t>LP-053209</t>
+  </si>
+  <si>
+    <t>LP-053252</t>
+  </si>
+  <si>
+    <t>LP-053258</t>
+  </si>
+  <si>
+    <t>LP-053304</t>
+  </si>
+  <si>
+    <t>LP-053418</t>
+  </si>
+  <si>
+    <t>LP-034807</t>
+  </si>
+  <si>
+    <t>LP-047231</t>
+  </si>
+  <si>
+    <t>LP-047283</t>
+  </si>
+  <si>
+    <t>LP-048855</t>
+  </si>
+  <si>
+    <t>LP-050005</t>
+  </si>
+  <si>
+    <t>LP-051088</t>
+  </si>
+  <si>
+    <t>LP-051089</t>
+  </si>
+  <si>
+    <t>LP-051757</t>
+  </si>
+  <si>
+    <t>LP-051895</t>
+  </si>
+  <si>
+    <t>LP-051994</t>
+  </si>
+  <si>
+    <t>LP-052078</t>
+  </si>
+  <si>
+    <t>LP-052205</t>
+  </si>
+  <si>
+    <t>LP-052268</t>
+  </si>
+  <si>
+    <t>LP-052270</t>
+  </si>
+  <si>
+    <t>LP-052271</t>
+  </si>
+  <si>
+    <t>LP-052272</t>
+  </si>
+  <si>
+    <t>LP-052538</t>
+  </si>
+  <si>
+    <t>LP-052568</t>
+  </si>
+  <si>
+    <t>LP-052588</t>
+  </si>
+  <si>
+    <t>LP-052590</t>
+  </si>
+  <si>
+    <t>LP-052602</t>
+  </si>
+  <si>
+    <t>LP-052610</t>
+  </si>
+  <si>
+    <t>LP-052667</t>
+  </si>
+  <si>
+    <t>LP-052692</t>
+  </si>
+  <si>
+    <t>LP-052742</t>
+  </si>
+  <si>
+    <t>LP-052762</t>
+  </si>
+  <si>
+    <t>LP-052776</t>
+  </si>
+  <si>
+    <t>LP-052778</t>
+  </si>
+  <si>
+    <t>LP-052811</t>
+  </si>
+  <si>
+    <t>LP-052832</t>
+  </si>
+  <si>
+    <t>LP-052834</t>
+  </si>
+  <si>
+    <t>LP-052835</t>
+  </si>
+  <si>
+    <t>LP-052840</t>
+  </si>
+  <si>
+    <t>LP-052846</t>
+  </si>
+  <si>
+    <t>LP-052849</t>
+  </si>
+  <si>
+    <t>LP-052883</t>
+  </si>
+  <si>
+    <t>LP-052886</t>
+  </si>
+  <si>
+    <t>LP-052926</t>
+  </si>
+  <si>
+    <t>LP-052948</t>
+  </si>
+  <si>
+    <t>LP-053183</t>
+  </si>
+  <si>
+    <t>LP-053190</t>
+  </si>
+  <si>
+    <t>LP-053285</t>
+  </si>
+  <si>
+    <t>LP-053287</t>
+  </si>
+  <si>
+    <t>LP-053288</t>
+  </si>
+  <si>
+    <t>LP-053360</t>
+  </si>
+  <si>
+    <t>LP-053462</t>
+  </si>
+  <si>
+    <t>LP-053525</t>
+  </si>
+  <si>
+    <t>LP-053605</t>
+  </si>
+  <si>
+    <t>LP-053652</t>
+  </si>
+  <si>
+    <t>LP-053661</t>
+  </si>
+  <si>
+    <t>LP-053710</t>
+  </si>
+  <si>
+    <t>LP-053795</t>
+  </si>
+  <si>
+    <t>LP-053813</t>
+  </si>
+  <si>
+    <t>LP-053815</t>
+  </si>
+  <si>
+    <t>LP-053820</t>
+  </si>
+  <si>
+    <t>LP-053823</t>
+  </si>
+  <si>
+    <t>LP-053841</t>
+  </si>
+  <si>
+    <t>LP-053857</t>
+  </si>
+  <si>
+    <t>LP-053858</t>
+  </si>
+  <si>
+    <t>LP-053864</t>
   </si>
 </sst>
 </file>
@@ -535,8 +673,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -550,191 +692,155 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
@@ -825,6 +931,236 @@
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B757D9-F41C-4885-8058-64D0AD250830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3D57D5-B04B-4600-A139-EB199EAE581F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="99">
   <si>
     <t>LP</t>
   </si>
@@ -31,6 +31,9 @@
     <t>LP-048854</t>
   </si>
   <si>
+    <t>Encerrado!</t>
+  </si>
+  <si>
     <t>LP-049319</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
   </si>
   <si>
     <t>LP-052014</t>
+  </si>
+  <si>
+    <t>Compromisso pendente!</t>
   </si>
   <si>
     <t>LP-052063</t>
@@ -675,10 +681,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -692,475 +694,607 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="B43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C48F9D-BEDB-4CD8-A690-D08D0AC5A1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9434D56A-A226-4312-B022-EBD82381AA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>LP</t>
   </si>
@@ -31,58 +31,313 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-049191</t>
-  </si>
-  <si>
-    <t>LP-052550</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-052747</t>
-  </si>
-  <si>
-    <t>LP-052751</t>
-  </si>
-  <si>
-    <t>LP-052774</t>
-  </si>
-  <si>
-    <t>LP-053054</t>
-  </si>
-  <si>
-    <t>LP-053053</t>
-  </si>
-  <si>
-    <t>LP-053080</t>
-  </si>
-  <si>
-    <t>LP-053083</t>
-  </si>
-  <si>
-    <t>LP-053084</t>
-  </si>
-  <si>
-    <t>LP-053085</t>
-  </si>
-  <si>
-    <t>LP-053086</t>
-  </si>
-  <si>
-    <t>LP-053092</t>
-  </si>
-  <si>
-    <t>LP-053096</t>
-  </si>
-  <si>
-    <t>LP-053097</t>
-  </si>
-  <si>
-    <t>LP-053098</t>
-  </si>
-  <si>
-    <t>LP-053419</t>
+    <t>LP-047465</t>
+  </si>
+  <si>
+    <t>LP-048897</t>
+  </si>
+  <si>
+    <t>LP-049755</t>
+  </si>
+  <si>
+    <t>LP-049885</t>
+  </si>
+  <si>
+    <t>LP-050304</t>
+  </si>
+  <si>
+    <t>LP-050763</t>
+  </si>
+  <si>
+    <t>LP-051074</t>
+  </si>
+  <si>
+    <t>LP-051442</t>
+  </si>
+  <si>
+    <t>LP-051657</t>
+  </si>
+  <si>
+    <t>LP-051661</t>
+  </si>
+  <si>
+    <t>LP-051698</t>
+  </si>
+  <si>
+    <t>LP-051755</t>
+  </si>
+  <si>
+    <t>LP-051984</t>
+  </si>
+  <si>
+    <t>LP-052191</t>
+  </si>
+  <si>
+    <t>LP-052193</t>
+  </si>
+  <si>
+    <t>LP-052539</t>
+  </si>
+  <si>
+    <t>LP-052557</t>
+  </si>
+  <si>
+    <t>LP-052558</t>
+  </si>
+  <si>
+    <t>LP-052561</t>
+  </si>
+  <si>
+    <t>LP-052563</t>
+  </si>
+  <si>
+    <t>LP-052639</t>
+  </si>
+  <si>
+    <t>LP-052641</t>
+  </si>
+  <si>
+    <t>LP-052659</t>
+  </si>
+  <si>
+    <t>LP-052665</t>
+  </si>
+  <si>
+    <t>LP-052715</t>
+  </si>
+  <si>
+    <t>LP-052743</t>
+  </si>
+  <si>
+    <t>LP-052761</t>
+  </si>
+  <si>
+    <t>LP-052763</t>
+  </si>
+  <si>
+    <t>LP-052775</t>
+  </si>
+  <si>
+    <t>LP-052795</t>
+  </si>
+  <si>
+    <t>LP-052845</t>
+  </si>
+  <si>
+    <t>LP-052892</t>
+  </si>
+  <si>
+    <t>LP-052911</t>
+  </si>
+  <si>
+    <t>LP-052968</t>
+  </si>
+  <si>
+    <t>LP-052998</t>
+  </si>
+  <si>
+    <t>LP-053043</t>
+  </si>
+  <si>
+    <t>LP-053088</t>
+  </si>
+  <si>
+    <t>LP-053141</t>
+  </si>
+  <si>
+    <t>LP-053152</t>
+  </si>
+  <si>
+    <t>LP-053202</t>
+  </si>
+  <si>
+    <t>LP-053269</t>
+  </si>
+  <si>
+    <t>LP-053273</t>
+  </si>
+  <si>
+    <t>LP-053274</t>
+  </si>
+  <si>
+    <t>LP-053282</t>
+  </si>
+  <si>
+    <t>LP-053284</t>
+  </si>
+  <si>
+    <t>LP-053323</t>
+  </si>
+  <si>
+    <t>LP-053334</t>
+  </si>
+  <si>
+    <t>LP-053347</t>
+  </si>
+  <si>
+    <t>LP-053355</t>
+  </si>
+  <si>
+    <t>LP-053358</t>
+  </si>
+  <si>
+    <t>LP-053359</t>
+  </si>
+  <si>
+    <t>LP-053367</t>
+  </si>
+  <si>
+    <t>LP-053368</t>
+  </si>
+  <si>
+    <t>LP-053520</t>
+  </si>
+  <si>
+    <t>LP-053581</t>
+  </si>
+  <si>
+    <t>LP-053582</t>
+  </si>
+  <si>
+    <t>LP-053583</t>
+  </si>
+  <si>
+    <t>LP-053584</t>
+  </si>
+  <si>
+    <t>LP-053585</t>
+  </si>
+  <si>
+    <t>LP-053664</t>
+  </si>
+  <si>
+    <t>LP-053666</t>
+  </si>
+  <si>
+    <t>LP-053667</t>
+  </si>
+  <si>
+    <t>LP-053706</t>
+  </si>
+  <si>
+    <t>LP-053716</t>
+  </si>
+  <si>
+    <t>LP-053784</t>
+  </si>
+  <si>
+    <t>LP-053785</t>
+  </si>
+  <si>
+    <t>LP-053788</t>
+  </si>
+  <si>
+    <t>LP-053811</t>
+  </si>
+  <si>
+    <t>LP-053812</t>
+  </si>
+  <si>
+    <t>LP-053874</t>
+  </si>
+  <si>
+    <t>LP-053876</t>
+  </si>
+  <si>
+    <t>LP-053877</t>
+  </si>
+  <si>
+    <t>LP-053967</t>
+  </si>
+  <si>
+    <t>LP-053993</t>
+  </si>
+  <si>
+    <t>LP-054057</t>
+  </si>
+  <si>
+    <t>LP-054058</t>
+  </si>
+  <si>
+    <t>LP-054059</t>
+  </si>
+  <si>
+    <t>LP-054076</t>
+  </si>
+  <si>
+    <t>LP-054087</t>
+  </si>
+  <si>
+    <t>LP-054201</t>
+  </si>
+  <si>
+    <t>LP-054205</t>
+  </si>
+  <si>
+    <t>LP-054219</t>
+  </si>
+  <si>
+    <t>LP-042349</t>
+  </si>
+  <si>
+    <t>LP-047508</t>
+  </si>
+  <si>
+    <t>LP-049209</t>
+  </si>
+  <si>
+    <t>LP-049346</t>
+  </si>
+  <si>
+    <t>LP-049509</t>
+  </si>
+  <si>
+    <t>LP-050227</t>
+  </si>
+  <si>
+    <t>LP-050399</t>
+  </si>
+  <si>
+    <t>LP-050431</t>
+  </si>
+  <si>
+    <t>LP-050540</t>
+  </si>
+  <si>
+    <t>LP-050652</t>
+  </si>
+  <si>
+    <t>LP-051430</t>
+  </si>
+  <si>
+    <t>LP-051435</t>
+  </si>
+  <si>
+    <t>LP-052198</t>
+  </si>
+  <si>
+    <t>LP-052327</t>
+  </si>
+  <si>
+    <t>LP-052624</t>
+  </si>
+  <si>
+    <t>LP-052732</t>
+  </si>
+  <si>
+    <t>LP-052769</t>
+  </si>
+  <si>
+    <t>LP-052770</t>
+  </si>
+  <si>
+    <t>LP-052894</t>
+  </si>
+  <si>
+    <t>LP-052912</t>
+  </si>
+  <si>
+    <t>LP-053614</t>
   </si>
 </sst>
 </file>
@@ -445,11 +700,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -469,128 +724,510 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>4</v>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9434D56A-A226-4312-B022-EBD82381AA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD7DCF3-F022-4860-9C00-C8274D81869B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="412">
   <si>
     <t>LP</t>
   </si>
@@ -338,6 +338,927 @@
   </si>
   <si>
     <t>LP-053614</t>
+  </si>
+  <si>
+    <t>LP-049351</t>
+  </si>
+  <si>
+    <t>LP-049864</t>
+  </si>
+  <si>
+    <t>LP-050412</t>
+  </si>
+  <si>
+    <t>LP-050432</t>
+  </si>
+  <si>
+    <t>LP-050467</t>
+  </si>
+  <si>
+    <t>LP-050653</t>
+  </si>
+  <si>
+    <t>LP-051151</t>
+  </si>
+  <si>
+    <t>LP-051317</t>
+  </si>
+  <si>
+    <t>LP-051447</t>
+  </si>
+  <si>
+    <t>LP-051487</t>
+  </si>
+  <si>
+    <t>LP-051699</t>
+  </si>
+  <si>
+    <t>LP-051789</t>
+  </si>
+  <si>
+    <t>LP-052219</t>
+  </si>
+  <si>
+    <t>LP-052221</t>
+  </si>
+  <si>
+    <t>LP-052236</t>
+  </si>
+  <si>
+    <t>LP-052238</t>
+  </si>
+  <si>
+    <t>LP-052249</t>
+  </si>
+  <si>
+    <t>LP-052252</t>
+  </si>
+  <si>
+    <t>LP-052313</t>
+  </si>
+  <si>
+    <t>LP-052317</t>
+  </si>
+  <si>
+    <t>LP-052318</t>
+  </si>
+  <si>
+    <t>LP-052378</t>
+  </si>
+  <si>
+    <t>LP-052678</t>
+  </si>
+  <si>
+    <t>LP-052730</t>
+  </si>
+  <si>
+    <t>LP-052734</t>
+  </si>
+  <si>
+    <t>LP-052785</t>
+  </si>
+  <si>
+    <t>LP-052802</t>
+  </si>
+  <si>
+    <t>LP-052895</t>
+  </si>
+  <si>
+    <t>LP-053094</t>
+  </si>
+  <si>
+    <t>LP-053100</t>
+  </si>
+  <si>
+    <t>LP-053102</t>
+  </si>
+  <si>
+    <t>LP-053341</t>
+  </si>
+  <si>
+    <t>LP-053342</t>
+  </si>
+  <si>
+    <t>LP-053567</t>
+  </si>
+  <si>
+    <t>LP-053625</t>
+  </si>
+  <si>
+    <t>LP-053626</t>
+  </si>
+  <si>
+    <t>LP-053797</t>
+  </si>
+  <si>
+    <t>LP-053798</t>
+  </si>
+  <si>
+    <t>LP-053832</t>
+  </si>
+  <si>
+    <t>LP-053905</t>
+  </si>
+  <si>
+    <t>LP-053916</t>
+  </si>
+  <si>
+    <t>LP-053943</t>
+  </si>
+  <si>
+    <t>LP-053950</t>
+  </si>
+  <si>
+    <t>LP-053954</t>
+  </si>
+  <si>
+    <t>LP-054159</t>
+  </si>
+  <si>
+    <t>LP-032933</t>
+  </si>
+  <si>
+    <t>LP-041323</t>
+  </si>
+  <si>
+    <t>LP-046039</t>
+  </si>
+  <si>
+    <t>LP-047201</t>
+  </si>
+  <si>
+    <t>LP-048028</t>
+  </si>
+  <si>
+    <t>LP-048364</t>
+  </si>
+  <si>
+    <t>LP-049121</t>
+  </si>
+  <si>
+    <t>LP-049613</t>
+  </si>
+  <si>
+    <t>LP-051440</t>
+  </si>
+  <si>
+    <t>LP-051489</t>
+  </si>
+  <si>
+    <t>LP-051490</t>
+  </si>
+  <si>
+    <t>LP-051499</t>
+  </si>
+  <si>
+    <t>LP-051525</t>
+  </si>
+  <si>
+    <t>LP-051720</t>
+  </si>
+  <si>
+    <t>LP-051722</t>
+  </si>
+  <si>
+    <t>LP-051751</t>
+  </si>
+  <si>
+    <t>LP-052104</t>
+  </si>
+  <si>
+    <t>LP-052294</t>
+  </si>
+  <si>
+    <t>LP-052472</t>
+  </si>
+  <si>
+    <t>LP-052503</t>
+  </si>
+  <si>
+    <t>LP-052564</t>
+  </si>
+  <si>
+    <t>LP-052601</t>
+  </si>
+  <si>
+    <t>LP-052689</t>
+  </si>
+  <si>
+    <t>LP-052690</t>
+  </si>
+  <si>
+    <t>LP-052829</t>
+  </si>
+  <si>
+    <t>LP-052830</t>
+  </si>
+  <si>
+    <t>LP-052847</t>
+  </si>
+  <si>
+    <t>LP-052852</t>
+  </si>
+  <si>
+    <t>LP-052853</t>
+  </si>
+  <si>
+    <t>LP-052854</t>
+  </si>
+  <si>
+    <t>LP-052858</t>
+  </si>
+  <si>
+    <t>LP-052872</t>
+  </si>
+  <si>
+    <t>LP-052925</t>
+  </si>
+  <si>
+    <t>LP-052936</t>
+  </si>
+  <si>
+    <t>LP-052951</t>
+  </si>
+  <si>
+    <t>LP-052972</t>
+  </si>
+  <si>
+    <t>LP-052973</t>
+  </si>
+  <si>
+    <t>LP-052975</t>
+  </si>
+  <si>
+    <t>LP-053142</t>
+  </si>
+  <si>
+    <t>LP-053144</t>
+  </si>
+  <si>
+    <t>LP-053196</t>
+  </si>
+  <si>
+    <t>LP-053214</t>
+  </si>
+  <si>
+    <t>LP-053271</t>
+  </si>
+  <si>
+    <t>LP-053272</t>
+  </si>
+  <si>
+    <t>LP-053332</t>
+  </si>
+  <si>
+    <t>LP-053350</t>
+  </si>
+  <si>
+    <t>LP-053351</t>
+  </si>
+  <si>
+    <t>LP-053354</t>
+  </si>
+  <si>
+    <t>LP-053356</t>
+  </si>
+  <si>
+    <t>LP-053370</t>
+  </si>
+  <si>
+    <t>LP-053371</t>
+  </si>
+  <si>
+    <t>LP-053372</t>
+  </si>
+  <si>
+    <t>LP-053373</t>
+  </si>
+  <si>
+    <t>LP-053374</t>
+  </si>
+  <si>
+    <t>LP-053376</t>
+  </si>
+  <si>
+    <t>LP-053379</t>
+  </si>
+  <si>
+    <t>LP-053380</t>
+  </si>
+  <si>
+    <t>LP-053381</t>
+  </si>
+  <si>
+    <t>LP-053515</t>
+  </si>
+  <si>
+    <t>LP-053516</t>
+  </si>
+  <si>
+    <t>LP-053517</t>
+  </si>
+  <si>
+    <t>LP-053518</t>
+  </si>
+  <si>
+    <t>LP-053519</t>
+  </si>
+  <si>
+    <t>LP-053606</t>
+  </si>
+  <si>
+    <t>LP-053968</t>
+  </si>
+  <si>
+    <t>LP-054060</t>
+  </si>
+  <si>
+    <t>LP-054230</t>
+  </si>
+  <si>
+    <t>LP-038305</t>
+  </si>
+  <si>
+    <t>LP-036769</t>
+  </si>
+  <si>
+    <t>LP-037400</t>
+  </si>
+  <si>
+    <t>LP-044938</t>
+  </si>
+  <si>
+    <t>LP-045873</t>
+  </si>
+  <si>
+    <t>LP-048181</t>
+  </si>
+  <si>
+    <t>LP-048182</t>
+  </si>
+  <si>
+    <t>LP-048183</t>
+  </si>
+  <si>
+    <t>LP-050712</t>
+  </si>
+  <si>
+    <t>LP-052102</t>
+  </si>
+  <si>
+    <t>LP-052103</t>
+  </si>
+  <si>
+    <t>LP-052453</t>
+  </si>
+  <si>
+    <t>LP-052603</t>
+  </si>
+  <si>
+    <t>LP-052649</t>
+  </si>
+  <si>
+    <t>LP-052650</t>
+  </si>
+  <si>
+    <t>LP-052668</t>
+  </si>
+  <si>
+    <t>LP-052716</t>
+  </si>
+  <si>
+    <t>LP-052740</t>
+  </si>
+  <si>
+    <t>LP-052809</t>
+  </si>
+  <si>
+    <t>LP-052810</t>
+  </si>
+  <si>
+    <t>LP-052831</t>
+  </si>
+  <si>
+    <t>LP-052857</t>
+  </si>
+  <si>
+    <t>LP-052887</t>
+  </si>
+  <si>
+    <t>LP-052890</t>
+  </si>
+  <si>
+    <t>LP-052891</t>
+  </si>
+  <si>
+    <t>LP-052955</t>
+  </si>
+  <si>
+    <t>LP-052970</t>
+  </si>
+  <si>
+    <t>LP-053015</t>
+  </si>
+  <si>
+    <t>LP-053135</t>
+  </si>
+  <si>
+    <t>LP-053148</t>
+  </si>
+  <si>
+    <t>LP-053161</t>
+  </si>
+  <si>
+    <t>LP-053189</t>
+  </si>
+  <si>
+    <t>LP-053193</t>
+  </si>
+  <si>
+    <t>LP-053194</t>
+  </si>
+  <si>
+    <t>LP-053290</t>
+  </si>
+  <si>
+    <t>LP-053337</t>
+  </si>
+  <si>
+    <t>LP-053338</t>
+  </si>
+  <si>
+    <t>LP-053352</t>
+  </si>
+  <si>
+    <t>LP-053353</t>
+  </si>
+  <si>
+    <t>LP-053357</t>
+  </si>
+  <si>
+    <t>LP-053375</t>
+  </si>
+  <si>
+    <t>LP-053452</t>
+  </si>
+  <si>
+    <t>LP-053535</t>
+  </si>
+  <si>
+    <t>LP-053552</t>
+  </si>
+  <si>
+    <t>LP-053553</t>
+  </si>
+  <si>
+    <t>LP-053554</t>
+  </si>
+  <si>
+    <t>LP-053555</t>
+  </si>
+  <si>
+    <t>LP-053572</t>
+  </si>
+  <si>
+    <t>LP-053653</t>
+  </si>
+  <si>
+    <t>LP-053654</t>
+  </si>
+  <si>
+    <t>LP-053655</t>
+  </si>
+  <si>
+    <t>LP-053656</t>
+  </si>
+  <si>
+    <t>LP-053662</t>
+  </si>
+  <si>
+    <t>LP-053663</t>
+  </si>
+  <si>
+    <t>LP-053665</t>
+  </si>
+  <si>
+    <t>LP-053708</t>
+  </si>
+  <si>
+    <t>LP-053715</t>
+  </si>
+  <si>
+    <t>LP-053744</t>
+  </si>
+  <si>
+    <t>LP-053782</t>
+  </si>
+  <si>
+    <t>LP-053836</t>
+  </si>
+  <si>
+    <t>LP-054130</t>
+  </si>
+  <si>
+    <t>LP-054397</t>
+  </si>
+  <si>
+    <t>LP-048755</t>
+  </si>
+  <si>
+    <t>LP-049178</t>
+  </si>
+  <si>
+    <t>LP-049340</t>
+  </si>
+  <si>
+    <t>LP-050176</t>
+  </si>
+  <si>
+    <t>LP-050242</t>
+  </si>
+  <si>
+    <t>LP-050309</t>
+  </si>
+  <si>
+    <t>LP-050409</t>
+  </si>
+  <si>
+    <t>LP-050416</t>
+  </si>
+  <si>
+    <t>LP-050421</t>
+  </si>
+  <si>
+    <t>LP-051505</t>
+  </si>
+  <si>
+    <t>LP-051691</t>
+  </si>
+  <si>
+    <t>LP-051694</t>
+  </si>
+  <si>
+    <t>LP-052218</t>
+  </si>
+  <si>
+    <t>LP-052247</t>
+  </si>
+  <si>
+    <t>LP-052250</t>
+  </si>
+  <si>
+    <t>LP-052251</t>
+  </si>
+  <si>
+    <t>LP-052713</t>
+  </si>
+  <si>
+    <t>LP-053034</t>
+  </si>
+  <si>
+    <t>LP-053119</t>
+  </si>
+  <si>
+    <t>LP-053613</t>
+  </si>
+  <si>
+    <t>LP-053615</t>
+  </si>
+  <si>
+    <t>LP-053617</t>
+  </si>
+  <si>
+    <t>LP-053909</t>
+  </si>
+  <si>
+    <t>LP-053914</t>
+  </si>
+  <si>
+    <t>LP-053928</t>
+  </si>
+  <si>
+    <t>LP-053946</t>
+  </si>
+  <si>
+    <t>LP-053948</t>
+  </si>
+  <si>
+    <t>LP-053958</t>
+  </si>
+  <si>
+    <t>LP-051779</t>
+  </si>
+  <si>
+    <t>LP-052387</t>
+  </si>
+  <si>
+    <t>LP-052796</t>
+  </si>
+  <si>
+    <t>LP-054196</t>
+  </si>
+  <si>
+    <t>LP-054197</t>
+  </si>
+  <si>
+    <t>LP-052569</t>
+  </si>
+  <si>
+    <t>LP-052591</t>
+  </si>
+  <si>
+    <t>LP-052660</t>
+  </si>
+  <si>
+    <t>LP-052693</t>
+  </si>
+  <si>
+    <t>LP-052954</t>
+  </si>
+  <si>
+    <t>LP-052966</t>
+  </si>
+  <si>
+    <t>LP-052971</t>
+  </si>
+  <si>
+    <t>LP-052980</t>
+  </si>
+  <si>
+    <t>LP-053041</t>
+  </si>
+  <si>
+    <t>LP-053042</t>
+  </si>
+  <si>
+    <t>LP-053143</t>
+  </si>
+  <si>
+    <t>LP-053169</t>
+  </si>
+  <si>
+    <t>LP-053171</t>
+  </si>
+  <si>
+    <t>LP-053197</t>
+  </si>
+  <si>
+    <t>LP-053198</t>
+  </si>
+  <si>
+    <t>LP-053324</t>
+  </si>
+  <si>
+    <t>LP-053344</t>
+  </si>
+  <si>
+    <t>LP-053474</t>
+  </si>
+  <si>
+    <t>LP-053475</t>
+  </si>
+  <si>
+    <t>LP-053377</t>
+  </si>
+  <si>
+    <t>LP-053378</t>
+  </si>
+  <si>
+    <t>LP-053787</t>
+  </si>
+  <si>
+    <t>LP-053873</t>
+  </si>
+  <si>
+    <t>LP-053875</t>
+  </si>
+  <si>
+    <t>LP-053899</t>
+  </si>
+  <si>
+    <t>LP-053900</t>
+  </si>
+  <si>
+    <t>LP-053922</t>
+  </si>
+  <si>
+    <t>LP-054126</t>
+  </si>
+  <si>
+    <t>LP-054144</t>
+  </si>
+  <si>
+    <t>LP-054225</t>
+  </si>
+  <si>
+    <t>LP-054271</t>
+  </si>
+  <si>
+    <t>LP-054284</t>
+  </si>
+  <si>
+    <t>LP-054285</t>
+  </si>
+  <si>
+    <t>LP-054351</t>
+  </si>
+  <si>
+    <t>LP-054369</t>
+  </si>
+  <si>
+    <t>LP-054446</t>
+  </si>
+  <si>
+    <t>LP-054447</t>
+  </si>
+  <si>
+    <t>LP-054452</t>
+  </si>
+  <si>
+    <t>LP-054504</t>
+  </si>
+  <si>
+    <t>LP-048266</t>
+  </si>
+  <si>
+    <t>LP-050665</t>
+  </si>
+  <si>
+    <t>LP-050726</t>
+  </si>
+  <si>
+    <t>LP-051510</t>
+  </si>
+  <si>
+    <t>LP-051807</t>
+  </si>
+  <si>
+    <t>LP-051809</t>
+  </si>
+  <si>
+    <t>LP-051811</t>
+  </si>
+  <si>
+    <t>LP-052225</t>
+  </si>
+  <si>
+    <t>LP-052397</t>
+  </si>
+  <si>
+    <t>LP-052399</t>
+  </si>
+  <si>
+    <t>LP-052963</t>
+  </si>
+  <si>
+    <t>LP-053064</t>
+  </si>
+  <si>
+    <t>LP-053109</t>
+  </si>
+  <si>
+    <t>LP-053265</t>
+  </si>
+  <si>
+    <t>LP-054212</t>
+  </si>
+  <si>
+    <t>LP-054347</t>
+  </si>
+  <si>
+    <t>LP-051120</t>
+  </si>
+  <si>
+    <t>LP-051764</t>
+  </si>
+  <si>
+    <t>LP-052147</t>
+  </si>
+  <si>
+    <t>LP-052415</t>
+  </si>
+  <si>
+    <t>LP-052666</t>
+  </si>
+  <si>
+    <t>LP-052813</t>
+  </si>
+  <si>
+    <t>LP-052965</t>
+  </si>
+  <si>
+    <t>LP-053369</t>
+  </si>
+  <si>
+    <t>LP-053476</t>
+  </si>
+  <si>
+    <t>LP-053481</t>
+  </si>
+  <si>
+    <t>LP-053547</t>
+  </si>
+  <si>
+    <t>LP-053548</t>
+  </si>
+  <si>
+    <t>LP-053549</t>
+  </si>
+  <si>
+    <t>LP-053576</t>
+  </si>
+  <si>
+    <t>LP-053579</t>
+  </si>
+  <si>
+    <t>LP-053580</t>
+  </si>
+  <si>
+    <t>LP-053586</t>
+  </si>
+  <si>
+    <t>LP-053612</t>
+  </si>
+  <si>
+    <t>LP-053632</t>
+  </si>
+  <si>
+    <t>LP-053745</t>
+  </si>
+  <si>
+    <t>LP-053790</t>
+  </si>
+  <si>
+    <t>LP-053791</t>
+  </si>
+  <si>
+    <t>LP-053792</t>
+  </si>
+  <si>
+    <t>LP-053793</t>
+  </si>
+  <si>
+    <t>LP-053978</t>
+  </si>
+  <si>
+    <t>LP-054039</t>
+  </si>
+  <si>
+    <t>LP-054138</t>
+  </si>
+  <si>
+    <t>LP-054141</t>
+  </si>
+  <si>
+    <t>LP-054142</t>
+  </si>
+  <si>
+    <t>LP-054143</t>
+  </si>
+  <si>
+    <t>LP-054146</t>
+  </si>
+  <si>
+    <t>LP-054223</t>
+  </si>
+  <si>
+    <t>LP-054279</t>
+  </si>
+  <si>
+    <t>LP-054281</t>
+  </si>
+  <si>
+    <t>LP-054516</t>
+  </si>
+  <si>
+    <t>LP-054522</t>
+  </si>
+  <si>
+    <t>LP-054523</t>
+  </si>
+  <si>
+    <t>LP-054526</t>
+  </si>
+  <si>
+    <t>LP-054567</t>
+  </si>
+  <si>
+    <t>LP-054583</t>
+  </si>
+  <si>
+    <t>LP-054641</t>
+  </si>
+  <si>
+    <t>LP-054644</t>
+  </si>
+  <si>
+    <t>LP-054657</t>
+  </si>
+  <si>
+    <t>LP-054699</t>
+  </si>
+  <si>
+    <t>LP-054713</t>
   </si>
 </sst>
 </file>
@@ -700,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B418"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1230,6 +2151,1576 @@
         <v>104</v>
       </c>
     </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE54DC25-EF9D-42BA-B9C9-13E316DCDB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D704A88F-207A-443F-A7A4-9528266650DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,156 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="362">
   <si>
     <t>LP</t>
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>LP-047465</t>
-  </si>
-  <si>
-    <t>Encerrado!</t>
-  </si>
-  <si>
-    <t>LP-048897</t>
-  </si>
-  <si>
-    <t>LP-049755</t>
-  </si>
-  <si>
-    <t>LP-049885</t>
-  </si>
-  <si>
-    <t>LP-050763</t>
-  </si>
-  <si>
-    <t>LP-051074</t>
-  </si>
-  <si>
-    <t>LP-051442</t>
-  </si>
-  <si>
-    <t>LP-051657</t>
-  </si>
-  <si>
-    <t>LP-051661</t>
-  </si>
-  <si>
-    <t>LP-051698</t>
-  </si>
-  <si>
-    <t>LP-051755</t>
-  </si>
-  <si>
-    <t>LP-051984</t>
-  </si>
-  <si>
-    <t>LP-052191</t>
-  </si>
-  <si>
-    <t>LP-052193</t>
-  </si>
-  <si>
-    <t>LP-052539</t>
-  </si>
-  <si>
-    <t>LP-052557</t>
-  </si>
-  <si>
-    <t>LP-052558</t>
-  </si>
-  <si>
-    <t>LP-052561</t>
-  </si>
-  <si>
-    <t>LP-052563</t>
-  </si>
-  <si>
-    <t>LP-052639</t>
-  </si>
-  <si>
-    <t>LP-052641</t>
-  </si>
-  <si>
-    <t>LP-052659</t>
-  </si>
-  <si>
-    <t>LP-052665</t>
-  </si>
-  <si>
-    <t>LP-052715</t>
-  </si>
-  <si>
-    <t>LP-052743</t>
-  </si>
-  <si>
-    <t>LP-052761</t>
-  </si>
-  <si>
-    <t>LP-052763</t>
-  </si>
-  <si>
-    <t>LP-052775</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-052795</t>
-  </si>
-  <si>
-    <t>LP-052845</t>
-  </si>
-  <si>
-    <t>LP-052892</t>
-  </si>
-  <si>
-    <t>LP-052911</t>
-  </si>
-  <si>
-    <t>LP-052968</t>
-  </si>
-  <si>
-    <t>LP-052998</t>
-  </si>
-  <si>
-    <t>LP-053043</t>
-  </si>
-  <si>
-    <t>LP-053088</t>
-  </si>
-  <si>
-    <t>LP-053141</t>
-  </si>
-  <si>
-    <t>LP-053152</t>
-  </si>
-  <si>
-    <t>LP-053202</t>
-  </si>
-  <si>
-    <t>LP-053269</t>
-  </si>
-  <si>
-    <t>LP-053273</t>
-  </si>
-  <si>
-    <t>LP-053274</t>
-  </si>
-  <si>
-    <t>LP-053282</t>
-  </si>
-  <si>
-    <t>LP-053284</t>
-  </si>
-  <si>
-    <t>LP-053323</t>
-  </si>
-  <si>
-    <t>LP-053334</t>
   </si>
   <si>
     <t>LP-053347</t>
@@ -1612,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B414"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1631,2203 +1487,1835 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B29" t="s">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B32" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B35" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B36" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B37" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B38" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B39" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>43</v>
       </c>
-      <c r="B41" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>44</v>
       </c>
-      <c r="B42" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>45</v>
       </c>
-      <c r="B43" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>46</v>
       </c>
-      <c r="B44" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>47</v>
       </c>
-      <c r="B45" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>48</v>
-      </c>
-      <c r="B46" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>292</v>
+        <v>227</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>327</v>
+        <v>273</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>275</v>
+        <v>334</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>352</v>
+        <v>292</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>355</v>
+        <v>293</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>356</v>
+        <v>294</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A370" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A371" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A372" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A373" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A375" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A376" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A377" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A378" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A379" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A380" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A381" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A382" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A383" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A384" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A385" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A386" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A391" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A392" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A394" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A395" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A396" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A397" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A398" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A399" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A400" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A401" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A402" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A403" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A404" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A405" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A406" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A407" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A408" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A409" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A410" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A411" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A412" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A413" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
-        <v>409</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D704A88F-207A-443F-A7A4-9528266650DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A145B3B-15E4-4675-B7B5-9C579F298097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1472,7 +1472,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A145B3B-15E4-4675-B7B5-9C579F298097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE45A890-2CDA-4D34-B874-1A19EC4D191F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="363">
   <si>
     <t>LP</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>LP-053347</t>
+  </si>
+  <si>
+    <t>LP finished!</t>
   </si>
   <si>
     <t>LP-053355</t>
@@ -1472,7 +1475,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1487,1835 +1490,1838 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE45A890-2CDA-4D34-B874-1A19EC4D191F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF77B2DB-AFB1-4183-B8FC-4D7C5F033F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="363">
   <si>
     <t>LP</t>
   </si>
@@ -1498,40 +1498,64 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -590,7 +590,11 @@
           <t>LP-053706</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -598,7 +602,11 @@
           <t>LP-053716</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -606,7 +614,11 @@
           <t>LP-053784</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -614,7 +626,11 @@
           <t>LP-053785</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -622,7 +638,11 @@
           <t>LP-053788</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -1302,7 +1302,11 @@
           <t>LP-052317</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Error!</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1310,7 +1314,11 @@
           <t>LP-052318</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1334,7 +1342,11 @@
           <t>LP-052730</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1342,7 +1354,11 @@
           <t>LP-052734</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1350,7 +1366,11 @@
           <t>LP-052785</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1358,7 +1378,11 @@
           <t>LP-052802</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1366,7 +1390,11 @@
           <t>LP-052895</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Already finished!</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1374,7 +1402,11 @@
           <t>LP-053094</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Already finished!</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1382,7 +1414,11 @@
           <t>LP-053100</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">

--- a/98 - Excels/Open-LPs.xlsx
+++ b/98 - Excels/Open-LPs.xlsx
@@ -1442,7 +1442,11 @@
           <t>LP-053342</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>LP finished!</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
